--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/neg_pos_orb.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/neg_pos_orb.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity Projects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Weapons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Weapons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219C08F5-9E0D-434A-9B48-3959F71320E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD11D0A-DA87-4D27-97AE-7D238D8271C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26" yWindow="4920" windowWidth="24685" windowHeight="14597" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5610" yWindow="750" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes_base" sheetId="1" r:id="rId1"/>
@@ -407,13 +407,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="24.640625" customWidth="1"/>
-    <col min="3" max="11" width="12.640625" customWidth="1"/>
+    <col min="1" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="11" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,7 +422,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -434,31 +434,31 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -466,7 +466,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -474,7 +474,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -482,7 +482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -490,18 +490,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -516,14 +516,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3CE5BFE-EF2D-4BBF-853C-AFB047A960B0}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="24.640625" customWidth="1"/>
-    <col min="5" max="5" width="48.640625" customWidth="1"/>
-    <col min="6" max="11" width="12.640625" customWidth="1"/>
+    <col min="1" max="4" width="24.625" customWidth="1"/>
+    <col min="5" max="5" width="48.625" customWidth="1"/>
+    <col min="6" max="11" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,7 +540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -558,7 +558,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -576,18 +576,18 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/neg_pos_orb.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/neg_pos_orb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Weapons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD11D0A-DA87-4D27-97AE-7D238D8271C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A605C334-46EE-4A77-8CBF-EEBA2418F895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5610" yWindow="750" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33450" yWindow="2130" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes_base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -84,6 +84,13 @@
   <si>
     <t>화염구 발사 속도 1 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileDuration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileDamageTime</t>
   </si>
 </sst>
 </file>
@@ -490,6 +497,22 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/neg_pos_orb.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/neg_pos_orb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Weapons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A605C334-46EE-4A77-8CBF-EEBA2418F895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C15A7F-9D1E-4C1D-987B-3290EC3DDC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33450" yWindow="2130" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="840" yWindow="735" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes_base" sheetId="1" r:id="rId1"/>
@@ -458,7 +458,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -470,7 +470,7 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -478,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -510,7 +510,7 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
